--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104754_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104754_W33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0233</v>
+        <v>4.9432</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3959</v>
+        <v>1.5667</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6274</v>
+        <v>3.3765</v>
       </c>
       <c r="G2" t="n">
         <v>2.3328</v>
@@ -610,13 +610,13 @@
         <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2823</v>
+        <v>0.2023</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1611</v>
+        <v>0.3319</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1213</v>
+        <v>-0.1297</v>
       </c>
       <c r="V2" t="n">
         <v>2.4082</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0165</v>
+        <v>4.2093</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8544</v>
+        <v>2.1306</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1621</v>
+        <v>2.0787</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4284</v>
+        <v>5.1651</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3624</v>
+        <v>4.5133</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5606</v>
+        <v>4.6024</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5233</v>
+        <v>0.1789</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0372</v>
+        <v>4.4235</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.989</v>
+        <v>0.5627</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5893</v>
+        <v>0.4729</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3997</v>
+        <v>0.0898</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5934</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1382</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7316</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.417</v>
+        <v>-0.7281</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8364</v>
+        <v>-0.1955</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5805</v>
+        <v>-0.5326</v>
       </c>
       <c r="V3" t="n">
-        <v>3.2684</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2684</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9654</v>
+        <v>3.567</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4199</v>
+        <v>3.0913</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5455</v>
+        <v>0.4757</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1651</v>
+        <v>-0.4284</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5133</v>
+        <v>-1.3624</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6024</v>
+        <v>1.5606</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1789</v>
+        <v>1.5233</v>
       </c>
       <c r="L4" t="n">
-        <v>4.4235</v>
+        <v>0.0372</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5627</v>
+        <v>-1.989</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4729</v>
+        <v>-0.5893</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0898</v>
+        <v>-1.3997</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2276</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2763</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0487</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.972</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9061</v>
+        <v>-0.5995</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0659</v>
+        <v>-0.2669</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5733</v>
+        <v>2.5176</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3722</v>
+        <v>1.2538</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2011</v>
+        <v>1.2638</v>
       </c>
       <c r="G5" t="n">
         <v>1.779</v>
@@ -844,13 +844,13 @@
         <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7292999999999999</v>
+        <v>-0.785</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0468</v>
+        <v>-0.1652</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6825</v>
+        <v>-0.6198</v>
       </c>
       <c r="V5" t="n">
         <v>0.1578</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.216</v>
+        <v>2.0835</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0614</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2774</v>
+        <v>3.0265</v>
       </c>
       <c r="G6" t="n">
         <v>1.6125</v>
@@ -922,13 +922,13 @@
         <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1954</v>
+        <v>0.0629</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1165</v>
+        <v>0.0019</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3119</v>
+        <v>0.0609</v>
       </c>
       <c r="V6" t="n">
         <v>1.3187</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0125</v>
+        <v>0.8941</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3139</v>
+        <v>0.1954</v>
       </c>
       <c r="F7" t="n">
         <v>0.6986</v>
@@ -1000,10 +1000,10 @@
         <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3159</v>
+        <v>-0.4343</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0926</v>
+        <v>-0.0258</v>
       </c>
       <c r="U7" t="n">
         <v>-0.4085</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9314</v>
+        <v>-0.7519</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4773</v>
+        <v>-0.3418</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4541</v>
+        <v>-0.4101</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4532</v>
+        <v>-2.2667</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0077</v>
+        <v>0.3475</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4455</v>
+        <v>-2.6142</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4789</v>
+        <v>-0.3182</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9653</v>
+        <v>1.2238</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5135999999999999</v>
+        <v>-1.542</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0257</v>
+        <v>-1.9485</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0424</v>
+        <v>-0.8763</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-1.0722</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6829</v>
+        <v>2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2763</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5934</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2252</v>
+        <v>-0.446</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1623</v>
+        <v>-0.1813</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3876</v>
+        <v>-0.2647</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4764</v>
+        <v>-0.3155</v>
       </c>
       <c r="W8" t="n">
         <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6342</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1143</v>
+        <v>-1.0185</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5787</v>
+        <v>-0.5958</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5356</v>
+        <v>-0.4227</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2667</v>
+        <v>1.4532</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3475</v>
+        <v>1.0077</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6142</v>
+        <v>0.4455</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3182</v>
+        <v>1.4789</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2238</v>
+        <v>0.9653</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.542</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9485</v>
+        <v>-0.0257</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8763</v>
+        <v>0.0424</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0722</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2763</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2763</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8084</v>
+        <v>-0.3123</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4182</v>
+        <v>0.0439</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3901</v>
+        <v>-0.3562</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3155</v>
+        <v>-1.4764</v>
       </c>
       <c r="W9" t="n">
         <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4733</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6667</v>
+        <v>-1.4055</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.746</v>
+        <v>-1.3906</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0793</v>
+        <v>-0.0148</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8929</v>
@@ -1234,13 +1234,13 @@
         <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1868</v>
+        <v>-0.9255</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9061</v>
+        <v>-0.5508</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2806</v>
+        <v>-0.3747</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8634</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2757</v>
+        <v>-2.6554</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3519</v>
+        <v>-0.8257</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9239</v>
+        <v>-1.8298</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6614</v>
@@ -1312,13 +1312,13 @@
         <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1368</v>
+        <v>-0.2429</v>
       </c>
       <c r="T11" t="n">
-        <v>0.232</v>
+        <v>-0.2418</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V11" t="n">
         <v>0.387</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2012</v>
+        <v>-3.7658</v>
       </c>
       <c r="E12" t="n">
         <v>-5.7847</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5835</v>
+        <v>2.0189</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2411</v>
@@ -1390,13 +1390,13 @@
         <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.139</v>
+        <v>-0.7036</v>
       </c>
       <c r="T12" t="n">
         <v>-0.465</v>
       </c>
       <c r="U12" t="n">
-        <v>0.326</v>
+        <v>-0.2386</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.617699999999999</v>
+        <v>8.617599999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.643699999999999</v>
+        <v>-1.6438</v>
       </c>
       <c r="F13" t="n">
         <v>10.2613</v>
@@ -1453,7 +1453,7 @@
         <v>-4.197399999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2075</v>
+        <v>0.2075000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-4.405</v>
@@ -1468,13 +1468,13 @@
         <v>20.4869</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.1791</v>
+        <v>-5.1789</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0471</v>
+        <v>-2.0472</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.1317</v>
+        <v>-3.1319</v>
       </c>
       <c r="V13" t="n">
         <v>3.110900000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5826</v>
+        <v>3.1786</v>
       </c>
       <c r="E14" t="n">
-        <v>2.474</v>
+        <v>1.8818</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1086</v>
+        <v>1.2968</v>
       </c>
       <c r="G14" t="n">
         <v>1.3343</v>
@@ -1546,13 +1546,13 @@
         <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1101</v>
+        <v>0.706</v>
       </c>
       <c r="T14" t="n">
-        <v>0.952</v>
+        <v>0.3597</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1581</v>
+        <v>0.3463</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7784</v>
+        <v>1.5485</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1683</v>
+        <v>0.8129</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6101</v>
+        <v>0.7356</v>
       </c>
       <c r="G15" t="n">
         <v>3.0863</v>
@@ -1624,13 +1624,13 @@
         <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0171</v>
+        <v>0.7872</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8355</v>
+        <v>0.4801</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1816</v>
+        <v>0.3071</v>
       </c>
       <c r="V15" t="n">
         <v>1.0895</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6932</v>
+        <v>1.1113</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2238</v>
+        <v>1.5791</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5305</v>
+        <v>-0.4678</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1894</v>
@@ -1702,13 +1702,13 @@
         <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2555</v>
+        <v>0.1626</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1394</v>
+        <v>0.2159</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1161</v>
+        <v>-0.0534</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3579</v>
+        <v>0.5077</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5736</v>
+        <v>-0.4551</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9315</v>
+        <v>0.9628</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5736</v>
@@ -1780,13 +1780,13 @@
         <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4762</v>
+        <v>0.626</v>
       </c>
       <c r="T17" t="n">
-        <v>0.232</v>
+        <v>0.3505</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2442</v>
+        <v>0.2755</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1568</v>
+        <v>-0.2959</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.2077</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0657</v>
+        <v>-0.0882</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0011</v>
+        <v>-1.9645</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7288</v>
+        <v>-1.6231</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2723</v>
+        <v>-0.3415</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5989</v>
+        <v>-0.1307</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4554</v>
+        <v>-0.7035</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.5728</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4022</v>
+        <v>-1.8339</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2734</v>
+        <v>-0.9196</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1287</v>
+        <v>-0.9143</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5934</v>
+        <v>2.0487</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5934</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>1.654</v>
+        <v>0.1648</v>
       </c>
       <c r="T18" t="n">
-        <v>0.464</v>
+        <v>-0.077</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1899</v>
+        <v>0.2418</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0895</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7739</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3155</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0479</v>
+        <v>-0.3545</v>
       </c>
       <c r="E19" t="n">
-        <v>0.279</v>
+        <v>0.7528</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3269</v>
+        <v>-1.1073</v>
       </c>
       <c r="G19" t="n">
         <v>2.0106</v>
@@ -1936,13 +1936,13 @@
         <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7641</v>
+        <v>-0.0708</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6273</v>
+        <v>-0.1535</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1368</v>
+        <v>0.0827</v>
       </c>
       <c r="V19" t="n">
         <v>-0.4733</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0716</v>
+        <v>-0.5332</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.994</v>
+        <v>0.3756</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1311</v>
+        <v>-2.0011</v>
       </c>
       <c r="H20" t="n">
-        <v>0.17</v>
+        <v>-1.7288</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.3012</v>
+        <v>-0.2723</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1406</v>
+        <v>-0.5989</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5581</v>
+        <v>-1.4554</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.6987</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9906</v>
+        <v>-1.4022</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3881</v>
+        <v>-0.2734</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6025</v>
+        <v>-1.1287</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9105</v>
+        <v>1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2763</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3658</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8122</v>
+        <v>0.9639</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1815</v>
+        <v>0.464</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3692</v>
+        <v>0.4999</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1578</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1578</v>
+        <v>-0.7739</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>J. SHACKELFORD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2504</v>
+        <v>-0.9915</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0368</v>
+        <v>-0.9393</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2136</v>
+        <v>-0.0522</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9645</v>
+        <v>0.7544</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6231</v>
+        <v>0.9881</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3415</v>
+        <v>-0.2337</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1307</v>
+        <v>0.1644</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7035</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5728</v>
+        <v>-0.7524</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8339</v>
+        <v>0.59</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9196</v>
+        <v>0.0713</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9143</v>
+        <v>0.5187</v>
       </c>
       <c r="P21" t="n">
-        <v>2.0487</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0487</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7897999999999999</v>
+        <v>0.5517</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9061</v>
+        <v>0.1531</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1163</v>
+        <v>0.3986</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5447</v>
+        <v>-0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5447</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8626</v>
+        <v>-2.5629</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9769</v>
+        <v>-4.3323</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1144</v>
+        <v>1.7693</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1293</v>
@@ -2248,13 +2248,13 @@
         <v>2.2763</v>
       </c>
       <c r="S23" t="n">
-        <v>1.6749</v>
+        <v>0.9745</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6034</v>
+        <v>0.2481</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0714</v>
+        <v>0.7264</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3187</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SHACKELFORD</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9217</v>
+        <v>-2.9284</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6499</v>
+        <v>-2.0912</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2718</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7544</v>
+        <v>-3.1311</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9881</v>
+        <v>0.17</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2337</v>
+        <v>-3.3012</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1644</v>
+        <v>-1.1406</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.5581</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7524</v>
+        <v>-1.6987</v>
       </c>
       <c r="M24" t="n">
-        <v>0.59</v>
+        <v>-1.9906</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0713</v>
+        <v>-0.3881</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5187</v>
+        <v>-1.6025</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3658</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5039</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1382</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3786</v>
+        <v>0.9555</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5576</v>
+        <v>1.1679</v>
       </c>
       <c r="U24" t="n">
-        <v>0.179</v>
+        <v>-0.2124</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9317</v>
+        <v>0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2472</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.767</v>
+        <v>-6.032</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.0962</v>
+        <v>-5.2671</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6708</v>
+        <v>-0.7649</v>
       </c>
       <c r="G25" t="n">
         <v>-3.9542</v>
@@ -2404,13 +2404,13 @@
         <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2194</v>
+        <v>-0.4844</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9061</v>
+        <v>-0.077</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3133</v>
+        <v>-0.4074</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2440,10 +2440,10 @@
         <v>-8.617700000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.2612</v>
+        <v>-10.2613</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6438</v>
+        <v>1.6436</v>
       </c>
       <c r="G26" t="n">
         <v>-8.409800000000001</v>
@@ -2452,7 +2452,7 @@
         <v>-9.7646</v>
       </c>
       <c r="I26" t="n">
-        <v>1.354700000000001</v>
+        <v>1.3547</v>
       </c>
       <c r="J26" t="n">
         <v>4.1974</v>
@@ -2473,7 +2473,7 @@
         <v>-3.0502</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.276299999999999</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q26" t="n">
         <v>-20.4868</v>
@@ -2482,10 +2482,10 @@
         <v>18.2106</v>
       </c>
       <c r="S26" t="n">
-        <v>5.1792</v>
+        <v>5.1791</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1319</v>
+        <v>3.1318</v>
       </c>
       <c r="U26" t="n">
         <v>2.0472</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104754_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104754_W33.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-2.8964</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104754_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.0069</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
